--- a/predictii BORLEANU TUDOR.xlsx
+++ b/predictii BORLEANU TUDOR.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tudorel\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://endava-my.sharepoint.com/personal/tudor-mihai_iakkel_endava_com/Documents/Desktop/Folderul/Personal Projects/Predictii Mondial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{560CD8FD-558C-4400-A7F7-BA6B694F42B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="8_{560CD8FD-558C-4400-A7F7-BA6B694F42B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98063A9A-AB49-4272-B953-74ABAE2833B2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -451,87 +451,93 @@
     <t>28.06.2026 05:00 UTC+3</t>
   </si>
   <si>
-    <t>2 1</t>
-  </si>
-  <si>
-    <t>2 2</t>
-  </si>
-  <si>
-    <t>1 0</t>
-  </si>
-  <si>
-    <t>1 3</t>
-  </si>
-  <si>
-    <t>0 3</t>
-  </si>
-  <si>
-    <t>1 2</t>
-  </si>
-  <si>
-    <t>6 0</t>
-  </si>
-  <si>
-    <t>1 1</t>
-  </si>
-  <si>
-    <t>3 0</t>
-  </si>
-  <si>
-    <t>7 1</t>
-  </si>
-  <si>
-    <t>3 2</t>
-  </si>
-  <si>
-    <t>1 4</t>
-  </si>
-  <si>
-    <t>4 1</t>
-  </si>
-  <si>
-    <t>2 0</t>
-  </si>
-  <si>
-    <t>0 2</t>
-  </si>
-  <si>
-    <t>0 0</t>
-  </si>
-  <si>
-    <t>3 1</t>
-  </si>
-  <si>
-    <t>5 1</t>
-  </si>
-  <si>
-    <t>4 0</t>
-  </si>
-  <si>
-    <t>3 3</t>
-  </si>
-  <si>
-    <t>0 1</t>
-  </si>
-  <si>
-    <t>2 5</t>
-  </si>
-  <si>
-    <t>6 7</t>
-  </si>
-  <si>
-    <t>0 5</t>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>1-0</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>6-0</t>
+  </si>
+  <si>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>7-1</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>2-0</t>
+  </si>
+  <si>
+    <t>0-2</t>
+  </si>
+  <si>
+    <t>0-0</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>0-1</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>0-5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="14">
@@ -670,52 +676,52 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1921,10 +1927,10 @@
       <c r="D2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1941,450 +1947,450 @@
       <c r="D3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="41" t="s">
         <v>145</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F5" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="12" t="s">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="42" t="s">
+        <v>145</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>147</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>149</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="44" t="s">
+        <v>150</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>145</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="44" t="s">
+        <v>151</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>152</v>
+      </c>
+      <c r="F14" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" s="46" t="s">
+        <v>153</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="45" t="s">
+        <v>154</v>
+      </c>
+      <c r="F16" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="8" t="s">
+      <c r="C17" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="F18" s="29" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" s="47" t="s">
+        <v>148</v>
+      </c>
+      <c r="F19" s="29" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" s="48" t="s">
+        <v>155</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="20" t="s">
+      <c r="C21" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" s="48" t="s">
+        <v>156</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="24" t="s">
+      <c r="C22" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" s="49" t="s">
+        <v>151</v>
+      </c>
+      <c r="F22" s="35" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="25" t="s">
+      <c r="C23" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" s="50" t="s">
         <v>150</v>
       </c>
-      <c r="F11" s="26" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="25" t="s">
+      <c r="F23" s="38" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="B24" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="D24" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="E24" s="50" t="s">
         <v>151</v>
       </c>
-      <c r="F13" s="26" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="28" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="F14" s="30" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15" s="33" t="s">
-        <v>153</v>
-      </c>
-      <c r="F15" s="34" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="E16" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="F16" s="30" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="B17" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="E17" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="F17" s="34" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="B18" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="D18" s="36" t="s">
-        <v>79</v>
-      </c>
-      <c r="E18" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="F18" s="38" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="B19" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="E19" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="F19" s="38" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="B20" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="C20" s="40" t="s">
-        <v>86</v>
-      </c>
-      <c r="D20" s="40" t="s">
-        <v>87</v>
-      </c>
-      <c r="E20" s="41" t="s">
-        <v>155</v>
-      </c>
-      <c r="F20" s="42" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="B21" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="E21" s="41" t="s">
-        <v>156</v>
-      </c>
-      <c r="F21" s="42" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="43" t="s">
-        <v>92</v>
-      </c>
-      <c r="B22" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" s="44" t="s">
-        <v>94</v>
-      </c>
-      <c r="E22" s="45" t="s">
-        <v>151</v>
-      </c>
-      <c r="F22" s="46" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="47" t="s">
-        <v>96</v>
-      </c>
-      <c r="B23" s="48" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" s="48" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" s="49" t="s">
-        <v>150</v>
-      </c>
-      <c r="F23" s="50" t="s">
+      <c r="F24" s="38" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="47" t="s">
-        <v>100</v>
-      </c>
-      <c r="B24" s="48" t="s">
-        <v>101</v>
-      </c>
-      <c r="C24" s="48" t="s">
-        <v>102</v>
-      </c>
-      <c r="D24" s="48" t="s">
-        <v>103</v>
-      </c>
-      <c r="E24" s="49" t="s">
-        <v>151</v>
-      </c>
-      <c r="F24" s="50" t="s">
-        <v>99</v>
-      </c>
-    </row>
     <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="43" t="s">
+      <c r="A25" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="B25" s="44" t="s">
+      <c r="B25" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="C25" s="44" t="s">
+      <c r="C25" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="D25" s="44" t="s">
+      <c r="D25" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="E25" s="45" t="s">
+      <c r="E25" s="49" t="s">
         <v>157</v>
       </c>
-      <c r="F25" s="46" t="s">
+      <c r="F25" s="35" t="s">
         <v>95</v>
       </c>
     </row>
@@ -2401,50 +2407,50 @@
       <c r="D26" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="39" t="s">
         <v>158</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="F27" s="10" t="s">
+      <c r="E27" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="F27" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="8" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2461,490 +2467,490 @@
       <c r="D29" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="B30" s="12" t="s">
+      <c r="F30" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="41" t="s">
+        <v>158</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="E34" s="44" t="s">
+        <v>153</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="43" t="s">
+        <v>151</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E37" s="44" t="s">
+        <v>146</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C38" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D38" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="E38" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="F38" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="D39" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="E39" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="F39" s="26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="B40" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="D40" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="E40" s="45" t="s">
+        <v>151</v>
+      </c>
+      <c r="F40" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B41" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="E41" s="46" t="s">
+        <v>157</v>
+      </c>
+      <c r="F41" s="26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="B42" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="D42" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="E42" s="48" t="s">
+        <v>159</v>
+      </c>
+      <c r="F42" s="32" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="B43" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C43" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D43" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="E43" s="47" t="s">
+        <v>161</v>
+      </c>
+      <c r="F43" s="29" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="B44" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C44" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="D44" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" s="47" t="s">
+        <v>162</v>
+      </c>
+      <c r="F44" s="29" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="B45" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="D45" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="E45" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="F45" s="32" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B46" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D46" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="E46" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="F46" s="35" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="B47" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="C47" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="D47" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="E47" s="50" t="s">
+        <v>158</v>
+      </c>
+      <c r="F47" s="38" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="B48" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="C48" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="D48" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="E48" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="F48" s="38" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="B49" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="D49" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="E49" s="49" t="s">
+        <v>159</v>
+      </c>
+      <c r="F49" s="35" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E50" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B51" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="16" t="s">
+      <c r="C51" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E51" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C52" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D52" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E52" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="F52" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E31" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="F31" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="D32" s="16" t="s">
+      <c r="D53" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="E32" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="F32" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="F33" s="14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="B34" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="D34" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="E34" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="F34" s="26" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="B35" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E35" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="F35" s="22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="D36" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="E36" s="21" t="s">
+      <c r="E53" s="42" t="s">
         <v>151</v>
       </c>
-      <c r="F36" s="22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="B37" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="C37" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D37" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="E37" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="F37" s="26" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="B38" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="C38" s="28" t="s">
-        <v>62</v>
-      </c>
-      <c r="D38" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="E38" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="F38" s="30" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="B39" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="C39" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="D39" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="E39" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="F39" s="34" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="B40" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C40" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="D40" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="E40" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="F40" s="30" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B41" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="C41" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="D41" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="E41" s="33" t="s">
-        <v>157</v>
-      </c>
-      <c r="F41" s="34" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="39" t="s">
-        <v>123</v>
-      </c>
-      <c r="B42" s="40" t="s">
-        <v>48</v>
-      </c>
-      <c r="C42" s="40" t="s">
-        <v>86</v>
-      </c>
-      <c r="D42" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="E42" s="41" t="s">
-        <v>159</v>
-      </c>
-      <c r="F42" s="42" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="35" t="s">
-        <v>124</v>
-      </c>
-      <c r="B43" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="C43" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="D43" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="E43" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="F43" s="38" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="B44" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C44" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="D44" s="36" t="s">
-        <v>79</v>
-      </c>
-      <c r="E44" s="37" t="s">
-        <v>162</v>
-      </c>
-      <c r="F44" s="38" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="B45" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="C45" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="D45" s="40" t="s">
-        <v>87</v>
-      </c>
-      <c r="E45" s="41" t="s">
-        <v>163</v>
-      </c>
-      <c r="F45" s="42" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="43" t="s">
-        <v>127</v>
-      </c>
-      <c r="B46" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="C46" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="D46" s="44" t="s">
-        <v>105</v>
-      </c>
-      <c r="E46" s="45" t="s">
-        <v>155</v>
-      </c>
-      <c r="F46" s="46" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="47" t="s">
-        <v>128</v>
-      </c>
-      <c r="B47" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="C47" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="D47" s="48" t="s">
-        <v>102</v>
-      </c>
-      <c r="E47" s="49" t="s">
-        <v>158</v>
-      </c>
-      <c r="F47" s="50" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="47" t="s">
-        <v>129</v>
-      </c>
-      <c r="B48" s="48" t="s">
-        <v>101</v>
-      </c>
-      <c r="C48" s="48" t="s">
-        <v>103</v>
-      </c>
-      <c r="D48" s="48" t="s">
-        <v>98</v>
-      </c>
-      <c r="E48" s="49" t="s">
-        <v>157</v>
-      </c>
-      <c r="F48" s="50" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="B49" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="C49" s="44" t="s">
-        <v>106</v>
-      </c>
-      <c r="D49" s="44" t="s">
-        <v>94</v>
-      </c>
-      <c r="E49" s="45" t="s">
-        <v>159</v>
-      </c>
-      <c r="F49" s="46" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="F50" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B51" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="B52" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C52" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D52" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E52" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="F52" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="B53" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C53" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="E53" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="F53" s="18" t="s">
+      <c r="F53" s="14" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2961,10 +2967,10 @@
       <c r="D54" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="E54" s="39" t="s">
         <v>163</v>
       </c>
-      <c r="F54" s="6" t="s">
+      <c r="F54" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2981,370 +2987,370 @@
       <c r="D55" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="E55" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="F55" s="6" t="s">
+      <c r="F55" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="19" t="s">
+      <c r="A56" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="B56" s="20" t="s">
+      <c r="B56" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C56" s="20" t="s">
+      <c r="C56" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="D56" s="20" t="s">
+      <c r="D56" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="E56" s="21" t="s">
+      <c r="E56" s="43" t="s">
         <v>157</v>
       </c>
-      <c r="F56" s="22" t="s">
+      <c r="F56" s="17" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="19" t="s">
+      <c r="A57" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="B57" s="20" t="s">
+      <c r="B57" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C57" s="20" t="s">
+      <c r="C57" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D57" s="20" t="s">
+      <c r="D57" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="E57" s="21" t="s">
+      <c r="E57" s="43" t="s">
         <v>150</v>
       </c>
-      <c r="F57" s="22" t="s">
+      <c r="F57" s="17" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="23" t="s">
+      <c r="A58" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="B58" s="24" t="s">
+      <c r="B58" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="C58" s="24" t="s">
+      <c r="C58" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="D58" s="24" t="s">
+      <c r="D58" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="E58" s="25" t="s">
+      <c r="E58" s="44" t="s">
         <v>158</v>
       </c>
-      <c r="F58" s="26" t="s">
+      <c r="F58" s="20" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="23" t="s">
+      <c r="A59" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="B59" s="24" t="s">
+      <c r="B59" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="C59" s="24" t="s">
+      <c r="C59" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="D59" s="24" t="s">
+      <c r="D59" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="E59" s="25" t="s">
+      <c r="E59" s="44" t="s">
         <v>147</v>
       </c>
-      <c r="F59" s="26" t="s">
+      <c r="F59" s="20" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="11" t="s">
+      <c r="A60" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="C60" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="12" t="s">
+      <c r="D60" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E60" s="13" t="s">
+      <c r="E60" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="F60" s="14" t="s">
+      <c r="F60" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="11" t="s">
+      <c r="A61" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B61" s="12" t="s">
+      <c r="B61" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D61" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E61" s="13" t="s">
+      <c r="E61" s="41" t="s">
         <v>163</v>
       </c>
-      <c r="F61" s="14" t="s">
+      <c r="F61" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="35" t="s">
+      <c r="A62" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="B62" s="36" t="s">
+      <c r="B62" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="C62" s="36" t="s">
+      <c r="C62" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D62" s="36" t="s">
+      <c r="D62" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="E62" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="F62" s="38" t="s">
+      <c r="E62" s="47" t="s">
+        <v>145</v>
+      </c>
+      <c r="F62" s="29" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="35" t="s">
+      <c r="A63" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="B63" s="36" t="s">
+      <c r="B63" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C63" s="36" t="s">
+      <c r="C63" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="D63" s="36" t="s">
+      <c r="D63" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="E63" s="37" t="s">
+      <c r="E63" s="47" t="s">
         <v>155</v>
       </c>
-      <c r="F63" s="38" t="s">
+      <c r="F63" s="29" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="27" t="s">
+      <c r="A64" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="B64" s="28" t="s">
+      <c r="B64" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="C64" s="28" t="s">
+      <c r="C64" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D64" s="28" t="s">
+      <c r="D64" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="E64" s="29" t="s">
+      <c r="E64" s="45" t="s">
         <v>163</v>
       </c>
-      <c r="F64" s="30" t="s">
+      <c r="F64" s="23" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="27" t="s">
+      <c r="A65" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="B65" s="28" t="s">
+      <c r="B65" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C65" s="28" t="s">
+      <c r="C65" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="D65" s="28" t="s">
+      <c r="D65" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="E65" s="29" t="s">
+      <c r="E65" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="F65" s="30" t="s">
+      <c r="F65" s="23" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="31" t="s">
+      <c r="A66" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="B66" s="32" t="s">
+      <c r="B66" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="C66" s="32" t="s">
+      <c r="C66" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="D66" s="32" t="s">
+      <c r="D66" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="E66" s="33" t="s">
+      <c r="E66" s="46" t="s">
         <v>150</v>
       </c>
-      <c r="F66" s="34" t="s">
+      <c r="F66" s="26" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="31" t="s">
+      <c r="A67" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="B67" s="32" t="s">
+      <c r="B67" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="C67" s="32" t="s">
+      <c r="C67" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="D67" s="32" t="s">
+      <c r="D67" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="E67" s="33" t="s">
+      <c r="E67" s="46" t="s">
         <v>147</v>
       </c>
-      <c r="F67" s="34" t="s">
+      <c r="F67" s="26" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="47" t="s">
+      <c r="A68" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="B68" s="48" t="s">
+      <c r="B68" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="C68" s="48" t="s">
+      <c r="C68" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="D68" s="48" t="s">
+      <c r="D68" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="E68" s="49" t="s">
+      <c r="E68" s="50" t="s">
         <v>164</v>
       </c>
-      <c r="F68" s="50" t="s">
+      <c r="F68" s="38" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="47" t="s">
+      <c r="A69" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="B69" s="48" t="s">
+      <c r="B69" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="C69" s="48" t="s">
+      <c r="C69" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="D69" s="48" t="s">
+      <c r="D69" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="E69" s="49" t="s">
+      <c r="E69" s="50" t="s">
         <v>150</v>
       </c>
-      <c r="F69" s="50" t="s">
+      <c r="F69" s="38" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="43" t="s">
+      <c r="A70" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="B70" s="44" t="s">
+      <c r="B70" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="C70" s="44" t="s">
+      <c r="C70" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="D70" s="44" t="s">
+      <c r="D70" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="E70" s="45" t="s">
+      <c r="E70" s="49" t="s">
         <v>153</v>
       </c>
-      <c r="F70" s="46" t="s">
+      <c r="F70" s="35" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="43" t="s">
+      <c r="A71" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="B71" s="44" t="s">
+      <c r="B71" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="C71" s="44" t="s">
+      <c r="C71" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="D71" s="44" t="s">
+      <c r="D71" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="E71" s="45" t="s">
+      <c r="E71" s="49" t="s">
         <v>165</v>
       </c>
-      <c r="F71" s="46" t="s">
+      <c r="F71" s="35" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="39" t="s">
+      <c r="A72" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="B72" s="40" t="s">
+      <c r="B72" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="C72" s="40" t="s">
+      <c r="C72" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="D72" s="40" t="s">
+      <c r="D72" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="E72" s="41" t="s">
+      <c r="E72" s="48" t="s">
         <v>157</v>
       </c>
-      <c r="F72" s="42" t="s">
+      <c r="F72" s="32" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="39" t="s">
+      <c r="A73" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="B73" s="40" t="s">
+      <c r="B73" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C73" s="40" t="s">
+      <c r="C73" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="D73" s="40" t="s">
+      <c r="D73" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="E73" s="41" t="s">
+      <c r="E73" s="48" t="s">
         <v>166</v>
       </c>
-      <c r="F73" s="42" t="s">
+      <c r="F73" s="32" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3355,4 +3361,10 @@
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{63de93b7-8949-4e3d-a08b-0d778f7f5cab}" enabled="1" method="Standard" siteId="{0b3fc178-b730-4e8b-9843-e81259237b77}" removed="0"/>
+</clbl:labelList>
 </file>